--- a/wellsfargo-salesforce.xlsx
+++ b/wellsfargo-salesforce.xlsx
@@ -150,13 +150,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.0" customWidth="true"/>
     <col min="2" max="2" width="23.0" customWidth="true"/>
     <col min="3" max="3" width="18.0" customWidth="true"/>
-    <col min="4" max="4" width="38.0" customWidth="true"/>
+    <col min="4" max="4" width="41.0" customWidth="true"/>
     <col min="5" max="5" width="40.0" customWidth="true"/>
     <col min="6" max="6" width="92.0" customWidth="true"/>
     <col min="7" max="7" width="24.0" customWidth="true"/>
@@ -553,52 +553,52 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AmsO3</t>
+          <t>003QP00001Cl4FI</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Aminata</t>
+          <t>Alicia</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Kargbo</t>
+          <t>Hurtt</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>aminatakeneddy1995@gmail.com</t>
+          <t>alicia.hurtt@gmail.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kargbo</t>
+          <t>WellsFargo - Feb 26 - Hurtt</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Western Area</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Linkedin</t>
         </is>
       </c>
       <c r="K7" s="3" t="b">
@@ -609,107 +609,107 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AgjNR</t>
+          <t>003QP00001AmsO3</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Aminata</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ammons</t>
+          <t>Kargbo</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ammonsalbert@comcast.net</t>
+          <t>aminatakeneddy1995@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ammons</t>
+          <t>WellsFargo - Feb 26 - Kargbo</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Western Area</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Polsky Entrepreneurship program</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="K8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AVFxQ</t>
+          <t>003QP00001AgjNR</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Ammons</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>bettertomorrow900@gmail.com</t>
+          <t>ammonsalbert@comcast.net</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Spencer</t>
+          <t>WellsFargo - Feb 26 - Ammons</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>In</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>The Impact Circle</t>
+          <t>Polsky Entrepreneurship program</t>
         </is>
       </c>
       <c r="K9" s="3" t="b">
@@ -735,44 +735,44 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12/6/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>003QP000013kfxC</t>
+          <t>003QP00001AVFxQ</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Dr. Brandon</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>bgraham@ourhbcusmatter.org</t>
+          <t>bettertomorrow900@gmail.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Graham</t>
+          <t>WellsFargo - Feb 26 - Spencer</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>In</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Truist Foundation LinkedIn</t>
+          <t>The Impact Circle</t>
         </is>
       </c>
       <c r="K10" s="3" t="b">
@@ -798,44 +798,44 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>12/6/2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQu0</t>
+          <t>003QP000013kfxC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>WILLIAM</t>
+          <t>Dr. Brandon</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DAVIS</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>bill.davis40@gmail.com</t>
+          <t>bgraham@ourhbcusmatter.org</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - DAVIS</t>
+          <t>WellsFargo - Feb 26 - Graham</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -850,55 +850,55 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Truist Foundation LinkedIn</t>
         </is>
       </c>
       <c r="K11" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>003QP000019M5Jf</t>
+          <t>003QP00001AMQu0</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tabitha</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Hitchye</t>
+          <t>DAVIS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>bsdcartsinstitute@gmail.com</t>
+          <t>bill.davis40@gmail.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hitchye</t>
+          <t>WellsFargo - Feb 26 - DAVIS</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -913,55 +913,55 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>I received an email from a representative from Wells Fargo.</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="K12" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BfHFG</t>
+          <t>003QP000019M5Jf</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Tabitha</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Hitchye</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>cc@lieselconsultingllc.com</t>
+          <t>bsdcartsinstitute@gmail.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Taylor</t>
+          <t>WellsFargo - Feb 26 - Hitchye</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -976,45 +976,45 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>I learned of this opportunity from a small veteran-owned and operated business college, Thomas Christian,   from RH&amp;C</t>
+          <t>I received an email from a representative from Wells Fargo.</t>
         </is>
       </c>
       <c r="K13" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12/14/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Baz69</t>
+          <t>003QP00001BfHFG</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Necole</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>contact@bemorebaddies.com</t>
+          <t>cc@lieselconsultingllc.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Jackson</t>
+          <t>WellsFargo - Feb 26 - Taylor</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Hello! I learned about the Wells Fargo Small Business Fellowship from Asya Brandt who is a Wells Fargo employee. When she was in college, she interne</t>
+          <t>I learned of this opportunity from a small veteran-owned and operated business college, Thomas Christian,   from RH&amp;C</t>
         </is>
       </c>
       <c r="K14" s="3" t="b">
@@ -1050,44 +1050,44 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/14/2025</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>003QP0000190O9Z</t>
+          <t>003QP00001Baz69</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Necole</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>contactnoirr@gmail.com</t>
+          <t>contact@bemorebaddies.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Edwards</t>
+          <t>WellsFargo - Feb 26 - Jackson</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Referred through email from “organization “center of Greater Baltimore Urban League pulse-Moving the mission forward.</t>
+          <t>Hello! I learned about the Wells Fargo Small Business Fellowship from Asya Brandt who is a Wells Fargo employee. When she was in college, she interne</t>
         </is>
       </c>
       <c r="K15" s="3" t="b">
@@ -1113,44 +1113,44 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQun</t>
+          <t>003QP00001AMQve</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Berger</t>
+          <t>Byrd</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>crystal@joinebo.com</t>
+          <t>contact@jbhconsults.net</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Berger</t>
+          <t>WellsFargo - Feb 26 - Byrd</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>I was on Instagram and connected via a paid promotion in my stories.</t>
+          <t>I was recruited from Casey and Sandra from Wells Fargo and Watson Institute.</t>
         </is>
       </c>
       <c r="K16" s="3" t="b">
@@ -1176,44 +1176,44 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>003QP000019p4Lg</t>
+          <t>003QP00001CaAnt</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Clarence</t>
+          <t>Shawnte</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Mckinnon</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>csmith@hopeexcel.com</t>
+          <t>contact@mckinnonscg.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Smith</t>
+          <t>WellsFargo - Feb 26 - Mckinnon</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1228,55 +1228,55 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Facebook advertisements for Wells Fargo</t>
+          <t>I came across a post about the fellowship organically on social media while reviewing opportunities relevant to Baltimore-based entrepreneurs.</t>
         </is>
       </c>
       <c r="K17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>003QP00000CCc95</t>
+          <t>003QP0000190O9Z</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dr. Darvincia</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Edwards</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>darvincia_warren@coredmv.org</t>
+          <t>contactnoirr@gmail.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Warren</t>
+          <t>WellsFargo - Feb 26 - Edwards</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Md</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1291,55 +1291,55 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>I was contacted by Casey Field, after my submission to the Ford Fellowship, sharing that I may be a food fit for this fellowship. I then attended the</t>
+          <t>Referred through email from “organization “center of Greater Baltimore Urban League pulse-Moving the mission forward.</t>
         </is>
       </c>
       <c r="K18" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>003QP000017oVVV</t>
+          <t>003QP00001AMQun</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Berger</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>david.street2@gmail.com</t>
+          <t>crystal@joinebo.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Street</t>
+          <t>WellsFargo - Feb 26 - Berger</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1354,55 +1354,55 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>I was encourged to apply after speaking with both Casey Margarite Field of the Watson Institute and Seanicca (Edwards) Herron, executive director of</t>
+          <t>I was on Instagram and connected via a paid promotion in my stories.</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>003QP000019oslu</t>
+          <t>003QP000019p4Lg</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Deidre</t>
+          <t>Clarence</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Bowman</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>debowman1087@gmail.com</t>
+          <t>csmith@hopeexcel.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bowman</t>
+          <t>WellsFargo - Feb 26 - Smith</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Facebook advertisements for Wells Fargo</t>
         </is>
       </c>
       <c r="K20" s="3" t="b">
@@ -1435,37 +1435,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>003QP000019q9Cq</t>
+          <t>003QP00000CCc95</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Dr. Darvincia</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>digicoremediallc@gmail.com</t>
+          <t>darvincia_warren@coredmv.org</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nelson</t>
+          <t>WellsFargo - Feb 26 - Warren</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>LEDC Non - Profit Organization, located in Arlington, VA</t>
+          <t>I was contacted by Casey Field, after my submission to the Ford Fellowship, sharing that I may be a food fit for this fellowship. I then attended the</t>
         </is>
       </c>
       <c r="K21" s="3" t="b">
@@ -1491,14 +1491,14 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>003QP000019SB7s</t>
+          <t>003QP000017oVVV</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1508,27 +1508,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>dkim242@chicagobooth.edu</t>
+          <t>david.street2@gmail.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kim</t>
+          <t>WellsFargo - Feb 26 - Street</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>AI Tool or chatbot</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>I was encourged to apply after speaking with both Casey Margarite Field of the Watson Institute and Seanicca (Edwards) Herron, executive director of</t>
         </is>
       </c>
       <c r="K22" s="3" t="b">
@@ -1554,39 +1554,39 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>003QP00001A81lW</t>
+          <t>003QP000019oslu</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Deitra</t>
+          <t>Deidre</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Bowman</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>each1save1@yahoo.com</t>
+          <t>debowman1087@gmail.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Bowman</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Alisha Sparks- There's Hope Inc.</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="K23" s="3" t="b">
@@ -1617,44 +1617,44 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AiAbi</t>
+          <t>003QP000019q9Cq</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Frances</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>frances@jurisledger.com</t>
+          <t>digicoremediallc@gmail.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Joseph</t>
+          <t>WellsFargo - Feb 26 - Nelson</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>A family member told me about the program. Babajide Solanke.</t>
+          <t>LEDC Non - Profit Organization, located in Arlington, VA</t>
         </is>
       </c>
       <c r="K24" s="3" t="b">
@@ -1680,39 +1680,39 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Z41S</t>
+          <t>003QP000019SB7s</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>haley@wrkwth.com</t>
+          <t>dkim242@chicagobooth.edu</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Garcia</t>
+          <t>WellsFargo - Feb 26 - Kim</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>AI Tool or chatbot</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Saw it on my linkedin feed from someone in my Chicago network</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="3" t="b">
@@ -1743,39 +1743,39 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>003QP00000lBsQF</t>
+          <t>003QP00001A81lW</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Hamayun</t>
+          <t>Deitra</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>hamayun.salarzai@gmail.com</t>
+          <t>each1save1@yahoo.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Khan</t>
+          <t>WellsFargo - Feb 26 - Williams</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Alisha Sparks- There's Hope Inc.</t>
         </is>
       </c>
       <c r="K26" s="3" t="b">
@@ -1806,44 +1806,44 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11/5/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>003QP000015kP3M</t>
+          <t>003QP00001CJBzf</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Haneef</t>
+          <t>Ebony</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>haneefhardy5@gmail.com</t>
+          <t>ekarim@embarkussolutions.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hardy</t>
+          <t>WellsFargo - Feb 26 - Karim</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Casey  from Watson Institute reached out to me directly via email and from there i did my own research about the program</t>
+          <t>Email from Casey Field @Watson</t>
         </is>
       </c>
       <c r="K27" s="3" t="b">
@@ -1869,44 +1869,44 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMRwG</t>
+          <t>003QP00001CKYcQ</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>DeAndre</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>hello@youarebrandworthy.com</t>
+          <t>flourishinglivesinvestmentgrp@gmail.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Walker</t>
+          <t>WellsFargo - Feb 26 - Daniels</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1921,55 +1921,55 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>I am on the email list</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="K28" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>003QP000017BLsc</t>
+          <t>003QP00001AiAbi</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Frances</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>hswmanagementllc@yahoo.com</t>
+          <t>frances@jurisledger.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nelson</t>
+          <t>WellsFargo - Feb 26 - Joseph</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1984,45 +1984,45 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Truist Fellowship</t>
+          <t>A family member told me about the program. Babajide Solanke.</t>
         </is>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>003QP000015SPrN</t>
+          <t>003QP00001AMRwM</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Kenyana</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Weaver</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>info@communitysparksolutions.org</t>
+          <t>gabriel.5g2v@gmail.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Weaver</t>
+          <t>WellsFargo - Feb 26 - Lee</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute IG page</t>
+          <t>I received an email about the fellowship.</t>
         </is>
       </c>
       <c r="K30" s="3" t="b">
@@ -2058,44 +2058,44 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>0033h0000176VvV</t>
+          <t>003QP00001BttD8</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cassandra</t>
+          <t>GAUTHAM</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>PASUPULETI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>info@elevationglobalmediagroup.com</t>
+          <t>gautham@biodesigninnovationlabs.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ferguson</t>
+          <t>WellsFargo - Feb 26 - PASUPULETI</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>I received a email from Casey Field.</t>
+          <t>HALCYON INCUBATOR</t>
         </is>
       </c>
       <c r="K31" s="3" t="b">
@@ -2121,44 +2121,44 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BapoL</t>
+          <t>003QP000019Z41S</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Frederick Kimani Anku</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kenner</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>info@gardeningandbeats.com</t>
+          <t>haley@wrkwth.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kenner</t>
+          <t>WellsFargo - Feb 26 - Garcia</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Sean Noyes and his supervisor from Building Bridges DC/11 street bridge project told me to apply since i'm building an education in DC to teach the n</t>
+          <t>Saw it on my linkedin feed from someone in my Chicago network</t>
         </is>
       </c>
       <c r="K32" s="3" t="b">
@@ -2184,39 +2184,39 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>003QP000002o7f0</t>
+          <t>003QP00000lBsQF</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Jade Nicole</t>
+          <t>Hamayun</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Neverdon Merritt</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>info@jmerrittconsulting.com</t>
+          <t>hamayun.salarzai@gmail.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Neverdon Merritt</t>
+          <t>WellsFargo - Feb 26 - Khan</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2236,45 +2236,45 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Newsletter from Casey and Sandra at Watson Institute.</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="K33" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>11/5/2025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>003QP000009zHjZ</t>
+          <t>003QP000015kP3M</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Hyacinth</t>
+          <t>Haneef</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>info@laundrybasketdelivery.com</t>
+          <t>haneefhardy5@gmail.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Tucker</t>
+          <t>WellsFargo - Feb 26 - Hardy</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Md</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Casey Margarite Field</t>
+          <t>Casey  from Watson Institute reached out to me directly via email and from there i did my own research about the program</t>
         </is>
       </c>
       <c r="K34" s="3" t="b">
@@ -2317,32 +2317,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BH3sH</t>
+          <t>003QP00001AMRwG</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Jona</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Siko</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>info@printstudiochi.com</t>
+          <t>hello@youarebrandworthy.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Siko</t>
+          <t>WellsFargo - Feb 26 - Walker</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2362,55 +2362,55 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Referred to from the City of Chicago treasury department and the Chicago Sky Foundation. Sharice Bradford and  Riley Hughes</t>
+          <t>I am on the email list</t>
         </is>
       </c>
       <c r="K35" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>003QP000019q0bx</t>
+          <t>003QP000017BLsc</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Kamara</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>info@thejollofbowl.com</t>
+          <t>hswmanagementllc@yahoo.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kamara</t>
+          <t>WellsFargo - Feb 26 - Nelson</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>I came across it on social media.</t>
+          <t>Truist Fellowship</t>
         </is>
       </c>
       <c r="K36" s="3" t="b">
@@ -2436,44 +2436,44 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>003QP00000X5kPe</t>
+          <t>003QP000016Hgzp</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Rhea</t>
+          <t>Sherry</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Hechanova</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>inquiries@papierdollfactory.com</t>
+          <t>immigration@hechanovalaw.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Daniels</t>
+          <t>WellsFargo - Feb 26 - Hechanova</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Sought programs designed to support small business owners with mentorship, capital access, and strategic growth resources. The Wells Fargo Fellowship</t>
+          <t>Ashley Rankin, a graduate of one of the Watson Institute's programs.</t>
         </is>
       </c>
       <c r="K37" s="3" t="b">
@@ -2499,44 +2499,44 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>003QP000019aiBN</t>
+          <t>003QP000015SPrN</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Isiuwa</t>
+          <t>Kenyana</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Igodan</t>
+          <t>Weaver</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>isiuwaigodan@gmail.com</t>
+          <t>info@communitysparksolutions.org</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Igodan</t>
+          <t>WellsFargo - Feb 26 - Weaver</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2551,45 +2551,45 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>My friend sent it to me</t>
+          <t>Watson Institute IG page</t>
         </is>
       </c>
       <c r="K38" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQv6</t>
+          <t>0033h0000176VvV</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Jakerya</t>
+          <t>Cassandra</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>jakeryapatton@gmail.com</t>
+          <t>info@elevationglobalmediagroup.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Randolph</t>
+          <t>WellsFargo - Feb 26 - Ferguson</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2614,55 +2614,55 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Casey &amp; Sandra Watson Institute</t>
+          <t>I received a email from Casey Field.</t>
         </is>
       </c>
       <c r="K39" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>003QP00001993XG</t>
+          <t>003QP00001BapoL</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Frederick Kimani Anku</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Kenner</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>jbrooks@unlimitedexpressionspllc.com</t>
+          <t>info@gardeningandbeats.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Brooks</t>
+          <t>WellsFargo - Feb 26 - Kenner</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>I found out about the fellowship through a Wells Fargo post on Instagram.</t>
+          <t>Sean Noyes and his supervisor from Building Bridges DC/11 street bridge project told me to apply since i'm building an education in DC to teach the n</t>
         </is>
       </c>
       <c r="K40" s="3" t="b">
@@ -2688,34 +2688,34 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>003QP000016y4QP</t>
+          <t>003QP000002o7f0</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Jade Nicole</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Martin Jr</t>
+          <t>Neverdon Merritt</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>johnny@ccdgroup.org</t>
+          <t>info@jmerrittconsulting.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Martin Jr</t>
+          <t>WellsFargo - Feb 26 - Neverdon Merritt</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Newsletter from Casey and Sandra at Watson Institute.</t>
         </is>
       </c>
       <c r="K41" s="3" t="b">
@@ -2751,39 +2751,39 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BR9rb</t>
+          <t>003QP000009zHjZ</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Hyacinth</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>join@4thecollective.com</t>
+          <t>info@laundrybasketdelivery.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Logan</t>
+          <t>WellsFargo - Feb 26 - Tucker</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Email newsletter</t>
+          <t>Casey Margarite Field</t>
         </is>
       </c>
       <c r="K42" s="3" t="b">
@@ -2814,44 +2814,44 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>003QP000019JH1E</t>
+          <t>003QP00001CJOIX</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Reginald</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Owens II</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>joyce@armooh-williams.com</t>
+          <t>info@lightbrightpub.com</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Owens II</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>I received a direct email communication from Marguerite Casey at casey@watson.is. I was not referred by any individual, organization, or social media</t>
+          <t>The Polsky Exchange</t>
         </is>
       </c>
       <c r="K43" s="3" t="b">
@@ -2877,34 +2877,34 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AHS9k</t>
+          <t>003QP00001BH3sH</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Maisha</t>
+          <t>Jona</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Siko</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>kabobitrestaurant@gmail.com</t>
+          <t>info@printstudiochi.com</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Oliver</t>
+          <t>WellsFargo - Feb 26 - Siko</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Il</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Isra Omar the Polsky center</t>
+          <t>Referred to from the City of Chicago treasury department and the Chicago Sky Foundation. Sharice Bradford and  Riley Hughes</t>
         </is>
       </c>
       <c r="K44" s="3" t="b">
@@ -2940,44 +2940,44 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12/5/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>003QP000018CwmK</t>
+          <t>003QP000019q0bx</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Kendra</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Woolridge</t>
+          <t>Kamara</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>kendra@janetandjo.com</t>
+          <t>info@thejollofbowl.com</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Woolridge</t>
+          <t>WellsFargo - Feb 26 - Kamara</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>I saw an advertisement for the program on Instagram.</t>
+          <t>I came across it on social media.</t>
         </is>
       </c>
       <c r="K45" s="3" t="b">
@@ -3003,44 +3003,44 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>003QP000016oVuN</t>
+          <t>003QP00000X5kPe</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Rhea</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Beckford</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>kevinfbeckford@gmail.com</t>
+          <t>inquiries@papierdollfactory.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Beckford</t>
+          <t>WellsFargo - Feb 26 - Daniels</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3055,55 +3055,55 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Email</t>
+          <t>Sought programs designed to support small business owners with mentorship, capital access, and strategic growth resources. The Wells Fargo Fellowship</t>
         </is>
       </c>
       <c r="K46" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Azz0J</t>
+          <t>003QP000019aiBN</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Keturah</t>
+          <t>Isiuwa</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Igodan</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>kkimbr58@yahoo.com</t>
+          <t>isiuwaigodan@gmail.com</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Alexander</t>
+          <t>WellsFargo - Feb 26 - Igodan</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3118,45 +3118,45 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>The Inner Circle powered by Wells Fargo and partnered with Sara Jakes Roberts Woman Evolved.</t>
+          <t>My friend sent it to me</t>
         </is>
       </c>
       <c r="K47" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L47" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>003QP000017yg7w</t>
+          <t>003QP00001AMQv6</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Jakerya</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>McCree</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>kree@akwrestlingfoundation.org</t>
+          <t>jakeryapatton@gmail.com</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - McCree</t>
+          <t>WellsFargo - Feb 26 - Randolph</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3181,55 +3181,55 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Casey Field, Senior Search Manager sent an email to inform me of the opportunity.</t>
+          <t>Casey &amp; Sandra Watson Institute</t>
         </is>
       </c>
       <c r="K48" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Ame1h</t>
+          <t>003QP00001993XG</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>krwms62@gmail.com</t>
+          <t>jbrooks@unlimitedexpressionspllc.com</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Brooks</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>I received an email from the Watson Institute and researched the opportunity further via social media and Wells Fargo’s website.</t>
+          <t>I found out about the fellowship through a Wells Fargo post on Instagram.</t>
         </is>
       </c>
       <c r="K49" s="3" t="b">
@@ -3255,34 +3255,34 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>003QP000019tNpc</t>
+          <t>003QP000016y4QP</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Seble</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Mamo</t>
+          <t>Martin Jr</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>laboscience954@gmail.com</t>
+          <t>johnny@ccdgroup.org</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Mamo</t>
+          <t>WellsFargo - Feb 26 - Martin Jr</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3292,70 +3292,70 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Contact person: Miss Seble Mamo and organization name: Laboscience Enterprise  YouTube: https://youtube.com/@seblemamo858?si=dbnsTuEbuf5AnT8p</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K50" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>003QP000017x9MC</t>
+          <t>003QP00001BR9rb</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Lance</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>lancec@letsfeast.co</t>
+          <t>join@4thecollective.com</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Cabral</t>
+          <t>WellsFargo - Feb 26 - Logan</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>through Instagram</t>
+          <t>Email newsletter</t>
         </is>
       </c>
       <c r="K51" s="3" t="b">
@@ -3381,44 +3381,44 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>003QP0000169CIy</t>
+          <t>003QP000019JH1E</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Lathonia</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>lathonia@justuscpp.org</t>
+          <t>joyce@armooh-williams.com</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bennett</t>
+          <t>WellsFargo - Feb 26 - Williams</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>US Minor Outlying Islands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>I received a direct email communication from Marguerite Casey at casey@watson.is. I was not referred by any individual, organization, or social media</t>
         </is>
       </c>
       <c r="K52" s="3" t="b">
@@ -3444,19 +3444,19 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11/6/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQuv</t>
+          <t>003QP00001AHS9k</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Denika</t>
+          <t>Maisha</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>luvlotsss@yahoo.com</t>
+          <t>kabobitrestaurant@gmail.com</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Il</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3496,70 +3496,70 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>I’m currently a Wells Fargo customer with an open bank account &amp; I was emailed! &amp; I associate with an organization who’s in a partnership with We</t>
+          <t>Isra Omar the Polsky center</t>
         </is>
       </c>
       <c r="K53" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/5/2025</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>003QP00000sQBDe</t>
+          <t>003QP00001Cn7lh</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Manju</t>
+          <t>Karina</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Rupani</t>
+          <t>de Souza</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>manjurupani@outlook.com</t>
+          <t>karinaromano12@gmail.com</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Rupani</t>
+          <t>WellsFargo - Feb 26 - de Souza</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Outreach</t>
+          <t>It's been a while since I've been chasing an opportunity to represent my city, connect and learn more about creating social impact. So I've been foll</t>
         </is>
       </c>
       <c r="K54" s="3" t="b">
@@ -3570,44 +3570,44 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>003QP000016pbZS</t>
+          <t>003QP000018CwmK</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Marilyn</t>
+          <t>Kendra</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Berchie-Gialamas</t>
+          <t>Woolridge</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>marilyn@trinitymaternalwellness.org</t>
+          <t>kendra@janetandjo.com</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Berchie-Gialamas</t>
+          <t>WellsFargo - Feb 26 - Woolridge</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>I saw an advertisement for the program on Instagram.</t>
         </is>
       </c>
       <c r="K55" s="3" t="b">
@@ -3633,102 +3633,102 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>003QP00000BiRW5</t>
+          <t>003QP000016oVuN</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Murangiri</t>
+          <t>Beckford</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>markmurangiri885@gmail.com</t>
+          <t>kevinfbeckford@gmail.com</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Murangiri</t>
+          <t>WellsFargo - Feb 26 - Beckford</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>opportunities for youth</t>
+          <t>Watson Institute Email</t>
         </is>
       </c>
       <c r="K56" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AC7fR</t>
+          <t>003QP00001Azz0J</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Keturah</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Picciola</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>melissap@lanechicago.org</t>
+          <t>kkimbr58@yahoo.com</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Picciola</t>
+          <t>WellsFargo - Feb 26 - Alexander</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>West Side Forward Social media account</t>
+          <t>The Inner Circle powered by Wells Fargo and partnered with Sara Jakes Roberts Woman Evolved.</t>
         </is>
       </c>
       <c r="K57" s="3" t="b">
@@ -3759,34 +3759,34 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>003QP0000197rRi</t>
+          <t>003QP000017yg7w</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Watyoka</t>
+          <t>McCree</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>michael@growwisewealthybuilders.com</t>
+          <t>kree@akwrestlingfoundation.org</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Watyoka</t>
+          <t>WellsFargo - Feb 26 - McCree</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Howard county</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Casey Margarite Field, Sandra Mancia they work at Watson  Institute ,they  reached out to my wife and my wife shared with me ,she knows that I am bus</t>
+          <t>Casey Field, Senior Search Manager sent an email to inform me of the opportunity.</t>
         </is>
       </c>
       <c r="K58" s="3" t="b">
@@ -3822,59 +3822,59 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>003QP00000xXdiD</t>
+          <t>003QP00001Ame1h</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>test n29</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>octubre monica</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>monica.solaresdc@gmail.com</t>
+          <t>krwms62@gmail.com</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Undecided - Feb 26 - octubre monica</t>
+          <t>WellsFargo - Feb 26 - Williams</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>wsta</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
+          <t>I received an email from the Watson Institute and researched the opportunity further via social media and Wells Fargo’s website.</t>
         </is>
       </c>
       <c r="K59" s="3" t="b">
@@ -3885,59 +3885,59 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>003QP00000xXdiD</t>
+          <t>003QP000019tNpc</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>test n29</t>
+          <t>Seble</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>octubre monica</t>
+          <t>Mamo</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>monica.solaresdc@gmail.com</t>
+          <t>laboscience954@gmail.com</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - octubre monica</t>
+          <t>WellsFargo - Feb 26 - Mamo</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>wsta</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
+          <t>Contact person: Miss Seble Mamo and organization name: Laboscience Enterprise  YouTube: https://youtube.com/@seblemamo858?si=dbnsTuEbuf5AnT8p</t>
         </is>
       </c>
       <c r="K60" s="3" t="b">
@@ -3948,44 +3948,44 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>003QP00001B4NAV</t>
+          <t>003QP000017x9MC</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Morenikeji</t>
+          <t>Lance</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ofo</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>morenikeji.ofo@gmail.com</t>
+          <t>lancec@letsfeast.co</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ofo</t>
+          <t>WellsFargo - Feb 26 - Cabral</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Md/ North America</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>I was referred by Harold Booker of the Greater Baltimore Urban League. In 2022, I was a recipient of the Pepsi Black Accelerator Program and consider</t>
+          <t>through Instagram</t>
         </is>
       </c>
       <c r="K61" s="3" t="b">
@@ -4011,34 +4011,34 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AAha6</t>
+          <t>003QP0000169CIy</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Moses</t>
+          <t>Lathonia</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>moses@mohallcommercialud.com</t>
+          <t>lathonia@justuscpp.org</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hall</t>
+          <t>WellsFargo - Feb 26 - Bennett</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US Minor Outlying Islands</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Facebook Ad</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="K62" s="3" t="b">
@@ -4074,44 +4074,44 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/6/2025</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>003QP000018bhdh</t>
+          <t>003QP00001AMQtf</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Tanya</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Gamble</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>msgbusiness4@gmail.com</t>
+          <t>legacy2916@gmail.com</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gamble</t>
+          <t>WellsFargo - Feb 26 - Taylor</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4126,55 +4126,55 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>A sponsored ad on facebook.</t>
+          <t>I received an email invitation from Casey Margarite Field in response to interest from a social media post.</t>
         </is>
       </c>
       <c r="K63" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11/23/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AEf6g</t>
+          <t>003QP00001AMQuv</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Atif</t>
+          <t>Denika</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Tate</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>musicfuture2010@yahoo.com</t>
+          <t>luvlotsss@yahoo.com</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Tate</t>
+          <t>WellsFargo - Feb 26 - Oliver</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4189,55 +4189,55 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>I was referred by Greater Washington Urban League</t>
+          <t>I’m currently a Wells Fargo customer with an open bank account &amp; I was emailed! &amp; I associate with an organization who’s in a partnership with We</t>
         </is>
       </c>
       <c r="K64" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>003QP000019oMyy</t>
+          <t>003QP00001Bw5F6</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Nya</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>nyaemmyco@gmail.com</t>
+          <t>manager@pickleforklockandkey.com</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Johnson</t>
+          <t>WellsFargo - Feb 26 - Smith</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>District Of Columbia</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>I saw it on Instagram and clicked for more information</t>
+          <t>Baltimore City Mayor's Office - Small &amp; Minority Business Advocacy &amp; Development</t>
         </is>
       </c>
       <c r="K65" s="3" t="b">
@@ -4263,44 +4263,44 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Zdlb</t>
+          <t>003QP00000sQBDe</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Manju</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Rupani</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ojohnson@kok.services</t>
+          <t>manjurupani@outlook.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Johnson</t>
+          <t>WellsFargo - Feb 26 - Rupani</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Facebook Group: Illinois Small Business Owners Network</t>
+          <t>Wells Fargo Outreach</t>
         </is>
       </c>
       <c r="K66" s="3" t="b">
@@ -4326,170 +4326,170 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Qrat</t>
+          <t>003QP000016pbZS</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Nhlanhla</t>
+          <t>Marilyn</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Magwaza</t>
+          <t>Berchie-Gialamas</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>president@apasa-npc.org.za</t>
+          <t>marilyn@trinitymaternalwellness.org</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Magwaza</t>
+          <t>WellsFargo - Feb 26 - Berchie-Gialamas</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>KwaZulu Natal</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>I found information through Facebook advertising</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="K67" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>003QP000019E00u</t>
+          <t>003QP00000BiRW5</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nyembe</t>
+          <t>Murangiri</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>rsa.nyembe@gmail.com</t>
+          <t>markmurangiri885@gmail.com</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nyembe</t>
+          <t>WellsFargo - Feb 26 - Murangiri</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Gauteng</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>opportunities for youth</t>
         </is>
       </c>
       <c r="K68" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>003QP000016y4Qk</t>
+          <t>003QP00001CkL5F</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Marufa</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Gale</t>
+          <t>Bhuiyan</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>santanagale214@gmail.com</t>
+          <t>marufa@hawaii.edu</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gale</t>
+          <t>WellsFargo - Feb 26 - Bhuiyan</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>I am subscribed to your email list.</t>
+          <t>I was Googling about Fellowships to join in the USA in 2026, and it appeared on the first page</t>
         </is>
       </c>
       <c r="K69" s="3" t="b">
@@ -4515,44 +4515,44 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>003QP000019wFp2</t>
+          <t>003QP00001AC7fR</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Picciola</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>sean@hustlersmba.com</t>
+          <t>melissap@lanechicago.org</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Long</t>
+          <t>WellsFargo - Feb 26 - Picciola</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>I recieved an email from Casey Field</t>
+          <t>West Side Forward Social media account</t>
         </is>
       </c>
       <c r="K70" s="3" t="b">
@@ -4578,44 +4578,44 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>003QP000016GLZM</t>
+          <t>003QP0000197rRi</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Seke</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Ballard</t>
+          <t>Watyoka</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>seke@betascore.ai</t>
+          <t>michael@growwisewealthybuilders.com</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ballard</t>
+          <t>WellsFargo - Feb 26 - Watyoka</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Howard county</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Lorenzo Thione from Gaingels suggested that I apply.</t>
+          <t>Casey Margarite Field, Sandra Mancia they work at Watson  Institute ,they  reached out to my wife and my wife shared with me ,she knows that I am bus</t>
         </is>
       </c>
       <c r="K71" s="3" t="b">
@@ -4641,59 +4641,59 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>11/7/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>003QP000018FDO5</t>
+          <t>003QP00000xXdiD</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>test n29</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>octubre monica</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>simonejterry@icloud.com</t>
+          <t>monica.solaresdc@gmail.com</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Terry</t>
+          <t>Undecided - Feb 26 - octubre monica</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>wsta</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>I learned about the fellowship through an entrepreneurial support network that regularly shares resources and opportunities for small business owners</t>
+          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
         </is>
       </c>
       <c r="K72" s="3" t="b">
@@ -4704,59 +4704,59 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>003QP000019SXoJ</t>
+          <t>003QP00000xXdiD</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Enoch</t>
+          <t>test n29</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>octubre monica</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>smithenoch3@gmail.com</t>
+          <t>monica.solaresdc@gmail.com</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Smith</t>
+          <t>WellsFargo - Feb 26 - octubre monica</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>wsta</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>I receive monthly information from Illinois. Grant Watch, and this information was provided for my review.</t>
+          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
         </is>
       </c>
       <c r="K73" s="3" t="b">
@@ -4767,59 +4767,59 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>11/30/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AisuY</t>
+          <t>003QP00001B4NAV</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Morenikeji</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Gyapong</t>
+          <t>Ofo</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>steveagenda1899@gmail.com</t>
+          <t>morenikeji.ofo@gmail.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gyapong</t>
+          <t>WellsFargo - Feb 26 - Ofo</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Ashanti</t>
+          <t>Md/ North America</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>I was referred by Harold Booker of the Greater Baltimore Urban League. In 2022, I was a recipient of the Pepsi Black Accelerator Program and consider</t>
         </is>
       </c>
       <c r="K74" s="3" t="b">
@@ -4830,39 +4830,39 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AfbJz</t>
+          <t>003QP00001AAha6</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Moses</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>taylormason@taylorstacoschicago.com</t>
+          <t>moses@mohallcommercialud.com</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Mason</t>
+          <t>WellsFargo - Feb 26 - Hall</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>I heard about this opportunity from Isra Omar from the Polsky Center.</t>
+          <t>Facebook Ad</t>
         </is>
       </c>
       <c r="K75" s="3" t="b">
@@ -4893,44 +4893,44 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BZbMC</t>
+          <t>003QP00001C9yX1</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>thomas</t>
+          <t>Ebony</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>christian</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>tchrist443@gmail.com</t>
+          <t>mothersonpurpose@gmail.com</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - christian</t>
+          <t>WellsFargo - Feb 26 - Gibson</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Hvac</t>
+          <t>instagram: opportunities for youth</t>
         </is>
       </c>
       <c r="K76" s="3" t="b">
@@ -4956,44 +4956,44 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AYscs</t>
+          <t>003QP000018bhdh</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Terri</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Evans</t>
+          <t>Gamble</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>terrievans27@gmail.com</t>
+          <t>msgbusiness4@gmail.com</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Evans</t>
+          <t>WellsFargo - Feb 26 - Gamble</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>I first learned about the Fellowship through the Polsky Center for Entrepreneurship and Innovation. Isra Omar at the Polsky Center shared the opportu</t>
+          <t>A sponsored ad on facebook.</t>
         </is>
       </c>
       <c r="K77" s="3" t="b">
@@ -5019,34 +5019,34 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>12/7/2025</t>
+          <t>11/23/2025</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BGk4x</t>
+          <t>003QP00001AEf6g</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Atif</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Bridgers</t>
+          <t>Tate</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>thecollectivesoul369@gmail.com</t>
+          <t>musicfuture2010@yahoo.com</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bridgers</t>
+          <t>WellsFargo - Feb 26 - Tate</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Anita Sewell</t>
+          <t>I was referred by Greater Washington Urban League</t>
         </is>
       </c>
       <c r="K78" s="3" t="b">
@@ -5082,44 +5082,44 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>003QP00000SLZB5</t>
+          <t>003QP00001CT2Jy</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Ticina</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>dormevil</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>ticina@creativiticustom.com</t>
+          <t>naturalserenityflow@gmail.com</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - dormevil</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5134,55 +5134,55 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>I was sent an email by the Watson Institute to apply.</t>
+          <t>I learned about the Wells Fargo Small Business Fellowship through the Watson Institute entrepreneurial ecosystem and small business support network.</t>
         </is>
       </c>
       <c r="K79" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>003QP000011Hc2z</t>
+          <t>003QP000019oMyy</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Nya</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>tom@peakampinstruments.com</t>
+          <t>nyaemmyco@gmail.com</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Wright</t>
+          <t>WellsFargo - Feb 26 - Johnson</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5197,25 +5197,25 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>I learned about the fellowship through a colleague who knew I was working on data center maintenance technology and recommended I explore opportuniti</t>
+          <t>I saw it on Instagram and clicked for more information</t>
         </is>
       </c>
       <c r="K80" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>003QP000019ZPFa</t>
+          <t>003QP000019Zdlb</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>transportation@kneservies.com</t>
+          <t>ojohnson@kok.services</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Just an advertising on Facebook.</t>
+          <t>Facebook Group: Illinois Small Business Owners Network</t>
         </is>
       </c>
       <c r="K81" s="3" t="b">
@@ -5278,37 +5278,37 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>003QP000017hZik</t>
+          <t>003QP00001CryOQ</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Trezell</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ragas</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>trezell@ragasconsulting.com</t>
+          <t>orders@mspsgfree.com</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ragas</t>
+          <t>WellsFargo - Feb 26 - Marsh</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5323,142 +5323,1276 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Gloria Nauden, Co-Founder, DC COMMUNITY DEVELOPMENT CONSORTIUM  It was sent to her by Casey Margarite Field and Sandra Mancia from Watson Institute</t>
+          <t>I received an email</t>
         </is>
       </c>
       <c r="K82" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L82" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>0033h00001K7vgw</t>
+          <t>003QP000019Qrat</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Nhlanhla</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Urassa</t>
+          <t>Magwaza</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>urassastanley89@gmail.com</t>
+          <t>president@apasa-npc.org.za</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Urassa</t>
+          <t>WellsFargo - Feb 26 - Magwaza</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>KwaZulu Natal</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Tanzania, the United Republic of</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Tanzania, the United Republic of</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Stanley urassa,  SETHI URA COMPANY LIMITED</t>
+          <t>I found information through Facebook advertising</t>
         </is>
       </c>
       <c r="K83" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>003QP000019E00u</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Nyembe</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>rsa.nyembe@gmail.com</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Nyembe</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>11/27/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>003QP000016y4Qk</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Santana</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Gale</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>santanagale214@gmail.com</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Gale</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>I am subscribed to your email list.</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>11/13/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>003QP000019wFp2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Sean</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>sean@hustlersmba.com</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Long</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>I recieved an email from Casey Field</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>12/3/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>003QP000016GLZM</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Seke</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Ballard</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>seke@betascore.ai</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Ballard</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Lorenzo Thione from Gaingels suggested that I apply.</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>11/7/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>003QP000003kVao</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Shana</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>OConners</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>shana@disrupttheimpossible.com</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - OConners</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Polsky Exchange</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>12/16/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>003QP000018FDO5</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Simone</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Terry</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>simonejterry@icloud.com</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Terry</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>I learned about the fellowship through an entrepreneurial support network that regularly shares resources and opportunities for small business owners</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>003QP000019SXoJ</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Enoch</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>smithenoch3@gmail.com</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Smith</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>I receive monthly information from Illinois. Grant Watch, and this information was provided for my review.</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>11/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AisuY</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Gyapong</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>steveagenda1899@gmail.com</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Gyapong</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Ashanti</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>12/8/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AfbJz</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>taylormason@taylorstacoschicago.com</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Mason</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>I heard about this opportunity from Isra Omar from the Polsky Center.</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>12/8/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001BZbMC</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>thomas</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>christian</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>tchrist443@gmail.com</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - christian</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Md</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Hvac</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AYscs</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Terri</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>terrievans27@gmail.com</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Evans</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>I first learned about the Fellowship through the Polsky Center for Entrepreneurship and Innovation. Isra Omar at the Polsky Center shared the opportu</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>12/7/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AMQbh</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Glenda</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>thecititeam@thecitilife.com</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Lee</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore City's Mayor's Office of Small and Minority Business Advocacy and Development Email dated December 12, 2025</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L95" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>12/16/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001BGk4x</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Bridgers</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>thecollectivesoul369@gmail.com</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Bridgers</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Anita Sewell</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>003QP00000SLZB5</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Ticina</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>ticina@creativiticustom.com</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Williams</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>I was sent an email by the Watson Institute to apply.</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>003QP000011Hc2z</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>tom@peakampinstruments.com</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Wright</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>il</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>I learned about the fellowship through a colleague who knew I was working on data center maintenance technology and recommended I explore opportuniti</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>003QP000019ZPFa</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>transportation@kneservies.com</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Johnson</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Social Media (Non Watson Institute Accounts)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Just an advertising on Facebook.</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>12/1/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>003QP000017hZik</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Trezell</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Ragas</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>trezell@ragasconsulting.com</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Ragas</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Gloria Nauden, Co-Founder, DC COMMUNITY DEVELOPMENT CONSORTIUM  It was sent to her by Casey Margarite Field and Sandra Mancia from Watson Institute</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>0033h00001K7vgw</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Stanley</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Urassa</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>urassastanley89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Urassa</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Kilimanjaro</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania, the United Republic of</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania, the United Republic of</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Stanley urassa,  SETHI URA COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>11/26/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
           <t>003QP00001AhhEq</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Paula</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Tripp</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>yourvipbox2024@gmail.com</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>WellsFargo - Feb 26 - Tripp</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Polsky Center at the University of Chicago</t>
         </is>
       </c>
-      <c r="K84" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="K102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>12/8/2025</t>
         </is>

--- a/wellsfargo-salesforce.xlsx
+++ b/wellsfargo-salesforce.xlsx
@@ -150,7 +150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.0" customWidth="true"/>
@@ -161,7 +161,7 @@
     <col min="6" max="6" width="92.0" customWidth="true"/>
     <col min="7" max="7" width="24.0" customWidth="true"/>
     <col min="8" max="8" width="34.0" customWidth="true"/>
-    <col min="9" max="9" width="34.0" customWidth="true"/>
+    <col min="9" max="9" width="35.0" customWidth="true"/>
     <col min="10" max="10" width="151.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="15.0" customWidth="true"/>
@@ -616,163 +616,163 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AmsO3</t>
+          <t>003QP00001D0ytv</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Aminata</t>
+          <t>Anita</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Kargbo</t>
+          <t>Sewell</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>aminatakeneddy1995@gmail.com</t>
+          <t>alsentllc@gmail.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kargbo</t>
+          <t>WellsFargo - Feb 26 - Sewell</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Western Area</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Sean Noyes - 11th Street Bridge Park</t>
         </is>
       </c>
       <c r="K8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>12/24/2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AgjNR</t>
+          <t>003QP00001AmsO3</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Aminata</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ammons</t>
+          <t>Kargbo</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ammonsalbert@comcast.net</t>
+          <t>aminatakeneddy1995@gmail.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ammons</t>
+          <t>WellsFargo - Feb 26 - Kargbo</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Western Area</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Polsky Entrepreneurship program</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="K9" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L9" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AVFxQ</t>
+          <t>003QP00001AgjNR</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Ammons</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>bettertomorrow900@gmail.com</t>
+          <t>ammonsalbert@comcast.net</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Spencer</t>
+          <t>WellsFargo - Feb 26 - Ammons</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>In</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>The Impact Circle</t>
+          <t>Polsky Entrepreneurship program</t>
         </is>
       </c>
       <c r="K10" s="3" t="b">
@@ -798,44 +798,44 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12/6/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>003QP000013kfxC</t>
+          <t>003QP00001AVFxQ</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Dr. Brandon</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>bgraham@ourhbcusmatter.org</t>
+          <t>bettertomorrow900@gmail.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Graham</t>
+          <t>WellsFargo - Feb 26 - Spencer</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>In</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Truist Foundation LinkedIn</t>
+          <t>The Impact Circle</t>
         </is>
       </c>
       <c r="K11" s="3" t="b">
@@ -861,44 +861,44 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10/22/2025</t>
+          <t>12/6/2025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQu0</t>
+          <t>003QP000013kfxC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>WILLIAM</t>
+          <t>Dr. Brandon</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DAVIS</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>bill.davis40@gmail.com</t>
+          <t>bgraham@ourhbcusmatter.org</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - DAVIS</t>
+          <t>WellsFargo - Feb 26 - Graham</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -913,55 +913,55 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Truist Foundation LinkedIn</t>
         </is>
       </c>
       <c r="K12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>10/22/2025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>003QP000019M5Jf</t>
+          <t>003QP00001AMQu0</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tabitha</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Hitchye</t>
+          <t>DAVIS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>bsdcartsinstitute@gmail.com</t>
+          <t>bill.davis40@gmail.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hitchye</t>
+          <t>WellsFargo - Feb 26 - DAVIS</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -976,55 +976,55 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>I received an email from a representative from Wells Fargo.</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="K13" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BfHFG</t>
+          <t>003QP000019M5Jf</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Tabitha</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Hitchye</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>cc@lieselconsultingllc.com</t>
+          <t>bsdcartsinstitute@gmail.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Taylor</t>
+          <t>WellsFargo - Feb 26 - Hitchye</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1039,45 +1039,45 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>I learned of this opportunity from a small veteran-owned and operated business college, Thomas Christian,   from RH&amp;C</t>
+          <t>I received an email from a representative from Wells Fargo.</t>
         </is>
       </c>
       <c r="K14" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12/14/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Baz69</t>
+          <t>003QP00001BfHFG</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Necole</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>contact@bemorebaddies.com</t>
+          <t>cc@lieselconsultingllc.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Jackson</t>
+          <t>WellsFargo - Feb 26 - Taylor</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Hello! I learned about the Wells Fargo Small Business Fellowship from Asya Brandt who is a Wells Fargo employee. When she was in college, she interne</t>
+          <t>I learned of this opportunity from a small veteran-owned and operated business college, Thomas Christian,   from RH&amp;C</t>
         </is>
       </c>
       <c r="K15" s="3" t="b">
@@ -1113,44 +1113,44 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/14/2025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQve</t>
+          <t>003QP00001Dubkv</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Byrd</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>contact@jbhconsults.net</t>
+          <t>cjharris.connect@gmail.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Byrd</t>
+          <t>WellsFargo - Feb 26 - Harris</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1165,55 +1165,55 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>I was recruited from Casey and Sandra from Wells Fargo and Watson Institute.</t>
+          <t>I was referred by  Isra Omar Senior Assistant Director, Small Business Growth Polsky Center for Entrepreneurship and Innovation | THE UNIVERSITY O</t>
         </is>
       </c>
       <c r="K16" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>1/1/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CaAnt</t>
+          <t>003QP00001Baz69</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Shawnte</t>
+          <t>Necole</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Mckinnon</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>contact@mckinnonscg.com</t>
+          <t>contact@bemorebaddies.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Mckinnon</t>
+          <t>WellsFargo - Feb 26 - Jackson</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1228,55 +1228,55 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>I came across a post about the fellowship organically on social media while reviewing opportunities relevant to Baltimore-based entrepreneurs.</t>
+          <t>Hello! I learned about the Wells Fargo Small Business Fellowship from Asya Brandt who is a Wells Fargo employee. When she was in college, she interne</t>
         </is>
       </c>
       <c r="K17" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>003QP0000190O9Z</t>
+          <t>003QP00001AMQve</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Edwards</t>
+          <t>Byrd</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>contactnoirr@gmail.com</t>
+          <t>contact@jbhconsults.net</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Edwards</t>
+          <t>WellsFargo - Feb 26 - Byrd</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1291,45 +1291,45 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Referred through email from “organization “center of Greater Baltimore Urban League pulse-Moving the mission forward.</t>
+          <t>I was recruited from Casey and Sandra from Wells Fargo and Watson Institute.</t>
         </is>
       </c>
       <c r="K18" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQun</t>
+          <t>003QP00001CaAnt</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Shawnte</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Berger</t>
+          <t>Mckinnon</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>crystal@joinebo.com</t>
+          <t>contact@mckinnonscg.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Berger</t>
+          <t>WellsFargo - Feb 26 - Mckinnon</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>I was on Instagram and connected via a paid promotion in my stories.</t>
+          <t>I came across a post about the fellowship organically on social media while reviewing opportunities relevant to Baltimore-based entrepreneurs.</t>
         </is>
       </c>
       <c r="K19" s="3" t="b">
@@ -1365,44 +1365,44 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>003QP000019p4Lg</t>
+          <t>003QP0000190O9Z</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Clarence</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Edwards</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>csmith@hopeexcel.com</t>
+          <t>contactnoirr@gmail.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Smith</t>
+          <t>WellsFargo - Feb 26 - Edwards</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Md</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Facebook advertisements for Wells Fargo</t>
+          <t>Referred through email from “organization “center of Greater Baltimore Urban League pulse-Moving the mission forward.</t>
         </is>
       </c>
       <c r="K20" s="3" t="b">
@@ -1428,44 +1428,44 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>003QP00000CCc95</t>
+          <t>003QP00001Dnvzh</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Dr. Darvincia</t>
+          <t>michael</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>ransome</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>darvincia_warren@coredmv.org</t>
+          <t>cravinflavas@gmail.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Warren</t>
+          <t>WellsFargo - Feb 26 - ransome</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1480,55 +1480,55 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>I was contacted by Casey Field, after my submission to the Ford Fellowship, sharing that I may be a food fit for this fellowship. I then attended the</t>
+          <t>Greater Washington Urban League</t>
         </is>
       </c>
       <c r="K21" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/31/2025</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>003QP000017oVVV</t>
+          <t>003QP00001AMQun</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Berger</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>david.street2@gmail.com</t>
+          <t>crystal@joinebo.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Street</t>
+          <t>WellsFargo - Feb 26 - Berger</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1543,55 +1543,55 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>I was encourged to apply after speaking with both Casey Margarite Field of the Watson Institute and Seanicca (Edwards) Herron, executive director of</t>
+          <t>I was on Instagram and connected via a paid promotion in my stories.</t>
         </is>
       </c>
       <c r="K22" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>003QP000019oslu</t>
+          <t>003QP000019p4Lg</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Deidre</t>
+          <t>Clarence</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Bowman</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>debowman1087@gmail.com</t>
+          <t>csmith@hopeexcel.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bowman</t>
+          <t>WellsFargo - Feb 26 - Smith</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Facebook advertisements for Wells Fargo</t>
         </is>
       </c>
       <c r="K23" s="3" t="b">
@@ -1624,37 +1624,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>003QP000019q9Cq</t>
+          <t>003QP00000CCc95</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Dr. Darvincia</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>digicoremediallc@gmail.com</t>
+          <t>darvincia_warren@coredmv.org</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nelson</t>
+          <t>WellsFargo - Feb 26 - Warren</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>LEDC Non - Profit Organization, located in Arlington, VA</t>
+          <t>I was contacted by Casey Field, after my submission to the Ford Fellowship, sharing that I may be a food fit for this fellowship. I then attended the</t>
         </is>
       </c>
       <c r="K24" s="3" t="b">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>003QP000019SB7s</t>
+          <t>003QP000017oVVV</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1697,27 +1697,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>dkim242@chicagobooth.edu</t>
+          <t>david.street2@gmail.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kim</t>
+          <t>WellsFargo - Feb 26 - Street</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>AI Tool or chatbot</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>I was encourged to apply after speaking with both Casey Margarite Field of the Watson Institute and Seanicca (Edwards) Herron, executive director of</t>
         </is>
       </c>
       <c r="K25" s="3" t="b">
@@ -1743,39 +1743,39 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>003QP00001A81lW</t>
+          <t>003QP000019oslu</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Deitra</t>
+          <t>Deidre</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Bowman</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>each1save1@yahoo.com</t>
+          <t>debowman1087@gmail.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Bowman</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Alisha Sparks- There's Hope Inc.</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="K26" s="3" t="b">
@@ -1806,44 +1806,44 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CJBzf</t>
+          <t>003QP00001DjqsE</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Ebony</t>
+          <t>Destorian</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Karim</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ekarim@embarkussolutions.com</t>
+          <t>destorian@yahoo.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Karim</t>
+          <t>WellsFargo - Feb 26 - Cash</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Email from Casey Field @Watson</t>
+          <t>Dr. Derrick Standifer via mastermind group</t>
         </is>
       </c>
       <c r="K27" s="3" t="b">
@@ -1869,44 +1869,44 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/30/2025</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CKYcQ</t>
+          <t>003QP000019q9Cq</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>DeAndre</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>flourishinglivesinvestmentgrp@gmail.com</t>
+          <t>digicoremediallc@gmail.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Daniels</t>
+          <t>WellsFargo - Feb 26 - Nelson</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1921,55 +1921,55 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LEDC Non - Profit Organization, located in Arlington, VA</t>
         </is>
       </c>
       <c r="K28" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L28" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AiAbi</t>
+          <t>003QP000019SB7s</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Frances</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>frances@jurisledger.com</t>
+          <t>dkim242@chicagobooth.edu</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Joseph</t>
+          <t>WellsFargo - Feb 26 - Kim</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>AI Tool or chatbot</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1984,55 +1984,55 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>A family member told me about the program. Babajide Solanke.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K29" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L29" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMRwM</t>
+          <t>003QP00001CwIZr</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Donald</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Terry Jr</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>gabriel.5g2v@gmail.com</t>
+          <t>donald.terryjr@gmail.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Lee</t>
+          <t>WellsFargo - Feb 26 - Terry Jr</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2047,55 +2047,55 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>I received an email about the fellowship.</t>
+          <t>Family Friend suggest this fellowship to me (Shawn Parker, Owner/Operator, Connie's Chicken and Waffles)</t>
         </is>
       </c>
       <c r="K30" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BttD8</t>
+          <t>003QP00001A81lW</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GAUTHAM</t>
+          <t>Deitra</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>PASUPULETI</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>gautham@biodesigninnovationlabs.com</t>
+          <t>each1save1@yahoo.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - PASUPULETI</t>
+          <t>WellsFargo - Feb 26 - Williams</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>HALCYON INCUBATOR</t>
+          <t>Alisha Sparks- There's Hope Inc.</t>
         </is>
       </c>
       <c r="K31" s="3" t="b">
@@ -2121,39 +2121,39 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Z41S</t>
+          <t>003QP00001CJBzf</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Ebony</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Karim</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>haley@wrkwth.com</t>
+          <t>ekarim@embarkussolutions.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Garcia</t>
+          <t>WellsFargo - Feb 26 - Karim</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Saw it on my linkedin feed from someone in my Chicago network</t>
+          <t>Email from Casey Field @Watson</t>
         </is>
       </c>
       <c r="K32" s="3" t="b">
@@ -2184,39 +2184,39 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>003QP00000lBsQF</t>
+          <t>003QP00001CKYcQ</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Hamayun</t>
+          <t>DeAndre</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>hamayun.salarzai@gmail.com</t>
+          <t>flourishinglivesinvestmentgrp@gmail.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Khan</t>
+          <t>WellsFargo - Feb 26 - Daniels</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="K33" s="3" t="b">
@@ -2247,34 +2247,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11/5/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>003QP000015kP3M</t>
+          <t>003QP00001AiAbi</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Haneef</t>
+          <t>Frances</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>haneefhardy5@gmail.com</t>
+          <t>frances@jurisledger.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hardy</t>
+          <t>WellsFargo - Feb 26 - Joseph</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2299,45 +2299,45 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Casey  from Watson Institute reached out to me directly via email and from there i did my own research about the program</t>
+          <t>A family member told me about the program. Babajide Solanke.</t>
         </is>
       </c>
       <c r="K34" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMRwG</t>
+          <t>003QP00001AMRwM</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>hello@youarebrandworthy.com</t>
+          <t>gabriel.5g2v@gmail.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Walker</t>
+          <t>WellsFargo - Feb 26 - Lee</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>I am on the email list</t>
+          <t>I received an email about the fellowship.</t>
         </is>
       </c>
       <c r="K35" s="3" t="b">
@@ -2373,44 +2373,44 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>003QP000017BLsc</t>
+          <t>003QP00001BttD8</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>GAUTHAM</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>PASUPULETI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>hswmanagementllc@yahoo.com</t>
+          <t>gautham@biodesigninnovationlabs.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nelson</t>
+          <t>WellsFargo - Feb 26 - PASUPULETI</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Truist Fellowship</t>
+          <t>HALCYON INCUBATOR</t>
         </is>
       </c>
       <c r="K36" s="3" t="b">
@@ -2436,44 +2436,44 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>003QP000016Hgzp</t>
+          <t>003QP000019Z41S</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Sherry</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Hechanova</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>immigration@hechanovalaw.com</t>
+          <t>haley@wrkwth.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hechanova</t>
+          <t>WellsFargo - Feb 26 - Garcia</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2488,55 +2488,55 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Ashley Rankin, a graduate of one of the Watson Institute's programs.</t>
+          <t>Saw it on my linkedin feed from someone in my Chicago network</t>
         </is>
       </c>
       <c r="K37" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>003QP000015SPrN</t>
+          <t>003QP00000lBsQF</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Kenyana</t>
+          <t>Hamayun</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Weaver</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>info@communitysparksolutions.org</t>
+          <t>hamayun.salarzai@gmail.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Weaver</t>
+          <t>WellsFargo - Feb 26 - Khan</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2551,55 +2551,55 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute IG page</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="K38" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11/5/2025</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>0033h0000176VvV</t>
+          <t>003QP000015kP3M</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cassandra</t>
+          <t>Haneef</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>info@elevationglobalmediagroup.com</t>
+          <t>haneefhardy5@gmail.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ferguson</t>
+          <t>WellsFargo - Feb 26 - Hardy</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Md</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>I received a email from Casey Field.</t>
+          <t>Casey  from Watson Institute reached out to me directly via email and from there i did my own research about the program</t>
         </is>
       </c>
       <c r="K39" s="3" t="b">
@@ -2625,44 +2625,44 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BapoL</t>
+          <t>003QP00001DIb8i</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Frederick Kimani Anku</t>
+          <t>Derrick</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Kenner</t>
+          <t>Standifer</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>info@gardeningandbeats.com</t>
+          <t>hello@lilarc.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kenner</t>
+          <t>WellsFargo - Feb 26 - Standifer</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Sean Noyes and his supervisor from Building Bridges DC/11 street bridge project told me to apply since i'm building an education in DC to teach the n</t>
+          <t>I am a member of a Mastermind Mind Group and Rachell Dumas has provided the resources!</t>
         </is>
       </c>
       <c r="K40" s="3" t="b">
@@ -2688,34 +2688,34 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>12/26/2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>003QP000002o7f0</t>
+          <t>003QP00001AMRwG</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Jade Nicole</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Neverdon Merritt</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>info@jmerrittconsulting.com</t>
+          <t>hello@youarebrandworthy.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Neverdon Merritt</t>
+          <t>WellsFargo - Feb 26 - Walker</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Newsletter from Casey and Sandra at Watson Institute.</t>
+          <t>I am on the email list</t>
         </is>
       </c>
       <c r="K41" s="3" t="b">
@@ -2751,44 +2751,44 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>003QP000009zHjZ</t>
+          <t>003QP000017BLsc</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Hyacinth</t>
+          <t>April</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>info@laundrybasketdelivery.com</t>
+          <t>hswmanagementllc@yahoo.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Tucker</t>
+          <t>WellsFargo - Feb 26 - Nelson</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Casey Margarite Field</t>
+          <t>Truist Fellowship</t>
         </is>
       </c>
       <c r="K42" s="3" t="b">
@@ -2814,44 +2814,44 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11/4/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CJOIX</t>
+          <t>003QP000016Hgzp</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Reginald</t>
+          <t>Sherry</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Owens II</t>
+          <t>Hechanova</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>info@lightbrightpub.com</t>
+          <t>immigration@hechanovalaw.com</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Owens II</t>
+          <t>WellsFargo - Feb 26 - Hechanova</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2866,11 +2866,11 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>The Polsky Exchange</t>
+          <t>Ashley Rankin, a graduate of one of the Watson Institute's programs.</t>
         </is>
       </c>
       <c r="K43" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="3" t="b">
         <v>0</v>
@@ -2884,37 +2884,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BH3sH</t>
+          <t>003QP000015SPrN</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Jona</t>
+          <t>Kenyana</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Siko</t>
+          <t>Weaver</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>info@printstudiochi.com</t>
+          <t>info@communitysparksolutions.org</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Siko</t>
+          <t>WellsFargo - Feb 26 - Weaver</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2929,50 +2929,50 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Referred to from the City of Chicago treasury department and the Chicago Sky Foundation. Sharice Bradford and  Riley Hughes</t>
+          <t>Watson Institute IG page</t>
         </is>
       </c>
       <c r="K44" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>003QP000019q0bx</t>
+          <t>0033h0000176VvV</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Cassandra</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Kamara</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>info@thejollofbowl.com</t>
+          <t>info@elevationglobalmediagroup.com</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Kamara</t>
+          <t>WellsFargo - Feb 26 - Ferguson</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>I came across it on social media.</t>
+          <t>I received a email from Casey Field.</t>
         </is>
       </c>
       <c r="K45" s="3" t="b">
@@ -3003,44 +3003,44 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>003QP00000X5kPe</t>
+          <t>003QP00001BapoL</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Rhea</t>
+          <t>Frederick Kimani Anku</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Daniels</t>
+          <t>Kenner</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>inquiries@papierdollfactory.com</t>
+          <t>info@gardeningandbeats.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Daniels</t>
+          <t>WellsFargo - Feb 26 - Kenner</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3055,55 +3055,55 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Sought programs designed to support small business owners with mentorship, capital access, and strategic growth resources. The Wells Fargo Fellowship</t>
+          <t>Sean Noyes and his supervisor from Building Bridges DC/11 street bridge project told me to apply since i'm building an education in DC to teach the n</t>
         </is>
       </c>
       <c r="K46" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>003QP000019aiBN</t>
+          <t>003QP000002o7f0</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Isiuwa</t>
+          <t>Jade Nicole</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Igodan</t>
+          <t>Neverdon Merritt</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>isiuwaigodan@gmail.com</t>
+          <t>info@jmerrittconsulting.com</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Igodan</t>
+          <t>WellsFargo - Feb 26 - Neverdon Merritt</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3118,50 +3118,50 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>My friend sent it to me</t>
+          <t>Newsletter from Casey and Sandra at Watson Institute.</t>
         </is>
       </c>
       <c r="K47" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQv6</t>
+          <t>003QP000009zHjZ</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Jakerya</t>
+          <t>Hyacinth</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>Tucker</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>jakeryapatton@gmail.com</t>
+          <t>info@laundrybasketdelivery.com</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Randolph</t>
+          <t>WellsFargo - Feb 26 - Tucker</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3181,55 +3181,55 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Casey &amp; Sandra Watson Institute</t>
+          <t>Casey Margarite Field</t>
         </is>
       </c>
       <c r="K48" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>003QP00001993XG</t>
+          <t>003QP00001CJOIX</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Reginald</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Owens II</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>jbrooks@unlimitedexpressionspllc.com</t>
+          <t>info@lightbrightpub.com</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Brooks</t>
+          <t>WellsFargo - Feb 26 - Owens II</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>I found out about the fellowship through a Wells Fargo post on Instagram.</t>
+          <t>The Polsky Exchange</t>
         </is>
       </c>
       <c r="K49" s="3" t="b">
@@ -3255,44 +3255,44 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>003QP000016y4QP</t>
+          <t>003QP00001BH3sH</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Johnny</t>
+          <t>Jona</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Martin Jr</t>
+          <t>Siko</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>johnny@ccdgroup.org</t>
+          <t>info@printstudiochi.com</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Martin Jr</t>
+          <t>WellsFargo - Feb 26 - Siko</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3307,50 +3307,50 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Referred to from the City of Chicago treasury department and the Chicago Sky Foundation. Sharice Bradford and  Riley Hughes</t>
         </is>
       </c>
       <c r="K50" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>11/12/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BR9rb</t>
+          <t>003QP000019q0bx</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Kamara</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>join@4thecollective.com</t>
+          <t>info@thejollofbowl.com</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Logan</t>
+          <t>WellsFargo - Feb 26 - Kamara</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Email newsletter</t>
+          <t>I came across it on social media.</t>
         </is>
       </c>
       <c r="K51" s="3" t="b">
@@ -3381,44 +3381,44 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>003QP000019JH1E</t>
+          <t>003QP00000X5kPe</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Joyce</t>
+          <t>Rhea</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Daniels</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>joyce@armooh-williams.com</t>
+          <t>inquiries@papierdollfactory.com</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Daniels</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3433,55 +3433,55 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>I received a direct email communication from Marguerite Casey at casey@watson.is. I was not referred by any individual, organization, or social media</t>
+          <t>Sought programs designed to support small business owners with mentorship, capital access, and strategic growth resources. The Wells Fargo Fellowship</t>
         </is>
       </c>
       <c r="K52" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11/28/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AHS9k</t>
+          <t>003QP000019aiBN</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Maisha</t>
+          <t>Isiuwa</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Igodan</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>kabobitrestaurant@gmail.com</t>
+          <t>isiuwaigodan@gmail.com</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Oliver</t>
+          <t>WellsFargo - Feb 26 - Igodan</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Il</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3496,118 +3496,118 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Isra Omar the Polsky center</t>
+          <t>My friend sent it to me</t>
         </is>
       </c>
       <c r="K53" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L53" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>12/5/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Cn7lh</t>
+          <t>003QP00001AMQv6</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Karina</t>
+          <t>Jakerya</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>de Souza</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>karinaromano12@gmail.com</t>
+          <t>jakeryapatton@gmail.com</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - de Souza</t>
+          <t>WellsFargo - Feb 26 - Randolph</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>It's been a while since I've been chasing an opportunity to represent my city, connect and learn more about creating social impact. So I've been foll</t>
+          <t>Casey &amp; Sandra Watson Institute</t>
         </is>
       </c>
       <c r="K54" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>003QP000018CwmK</t>
+          <t>003QP00001993XG</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Kendra</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Woolridge</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>kendra@janetandjo.com</t>
+          <t>jbrooks@unlimitedexpressionspllc.com</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Woolridge</t>
+          <t>WellsFargo - Feb 26 - Brooks</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>I saw an advertisement for the program on Instagram.</t>
+          <t>I found out about the fellowship through a Wells Fargo post on Instagram.</t>
         </is>
       </c>
       <c r="K55" s="3" t="b">
@@ -3633,44 +3633,44 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>003QP000016oVuN</t>
+          <t>003QP00001DFEVm</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Joel</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Beckford</t>
+          <t>Ezugwu</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>kevinfbeckford@gmail.com</t>
+          <t>jezugwu95@gmail.com</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Beckford</t>
+          <t>WellsFargo - Feb 26 - Ezugwu</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Email</t>
+          <t>My business partner. Through INSTAGRAM &amp; WHATSAPP</t>
         </is>
       </c>
       <c r="K56" s="3" t="b">
@@ -3696,44 +3696,44 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>12/26/2025</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Azz0J</t>
+          <t>003QP000016y4QP</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Keturah</t>
+          <t>Johnny</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Martin Jr</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>kkimbr58@yahoo.com</t>
+          <t>johnny@ccdgroup.org</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Alexander</t>
+          <t>WellsFargo - Feb 26 - Martin Jr</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3748,50 +3748,50 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>The Inner Circle powered by Wells Fargo and partnered with Sara Jakes Roberts Woman Evolved.</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K57" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>11/12/2025</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>003QP000017yg7w</t>
+          <t>003QP00001BR9rb</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>McCree</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>kree@akwrestlingfoundation.org</t>
+          <t>join@4thecollective.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - McCree</t>
+          <t>WellsFargo - Feb 26 - Logan</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Casey Field, Senior Search Manager sent an email to inform me of the opportunity.</t>
+          <t>Email newsletter</t>
         </is>
       </c>
       <c r="K58" s="3" t="b">
@@ -3822,19 +3822,19 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Ame1h</t>
+          <t>003QP000019JH1E</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Joyce</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>krwms62@gmail.com</t>
+          <t>joyce@armooh-williams.com</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>I received an email from the Watson Institute and researched the opportunity further via social media and Wells Fargo’s website.</t>
+          <t>I received a direct email communication from Marguerite Casey at casey@watson.is. I was not referred by any individual, organization, or social media</t>
         </is>
       </c>
       <c r="K59" s="3" t="b">
@@ -3885,59 +3885,59 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>12/9/2025</t>
+          <t>11/28/2025</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>003QP000019tNpc</t>
+          <t>003QP00001AHS9k</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Seble</t>
+          <t>Maisha</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Mamo</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>laboscience954@gmail.com</t>
+          <t>kabobitrestaurant@gmail.com</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Mamo</t>
+          <t>WellsFargo - Feb 26 - Oliver</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Il</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Contact person: Miss Seble Mamo and organization name: Laboscience Enterprise  YouTube: https://youtube.com/@seblemamo858?si=dbnsTuEbuf5AnT8p</t>
+          <t>Isra Omar the Polsky center</t>
         </is>
       </c>
       <c r="K60" s="3" t="b">
@@ -3948,34 +3948,34 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>12/5/2025</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>003QP000017x9MC</t>
+          <t>003QP00001Cn7lh</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Lance</t>
+          <t>Karina</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Cabral</t>
+          <t>de Souza</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>lancec@letsfeast.co</t>
+          <t>karinaromano12@gmail.com</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Cabral</t>
+          <t>WellsFargo - Feb 26 - de Souza</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3985,22 +3985,22 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>through Instagram</t>
+          <t>It's been a while since I've been chasing an opportunity to represent my city, connect and learn more about creating social impact. So I've been foll</t>
         </is>
       </c>
       <c r="K61" s="3" t="b">
@@ -4011,44 +4011,44 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>11/19/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>003QP0000169CIy</t>
+          <t>003QP000018CwmK</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Lathonia</t>
+          <t>Kendra</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Woolridge</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>lathonia@justuscpp.org</t>
+          <t>kendra@janetandjo.com</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bennett</t>
+          <t>WellsFargo - Feb 26 - Woolridge</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>US Minor Outlying Islands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>I saw an advertisement for the program on Instagram.</t>
         </is>
       </c>
       <c r="K62" s="3" t="b">
@@ -4074,34 +4074,34 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11/6/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQtf</t>
+          <t>003QP000016oVuN</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Beckford</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>legacy2916@gmail.com</t>
+          <t>kevinfbeckford@gmail.com</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Taylor</t>
+          <t>WellsFargo - Feb 26 - Beckford</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4126,45 +4126,45 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>I received an email invitation from Casey Margarite Field in response to interest from a social media post.</t>
+          <t>Watson Institute Email</t>
         </is>
       </c>
       <c r="K63" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQuv</t>
+          <t>003QP00001Azz0J</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Denika</t>
+          <t>Keturah</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>luvlotsss@yahoo.com</t>
+          <t>kkimbr58@yahoo.com</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Oliver</t>
+          <t>WellsFargo - Feb 26 - Alexander</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4189,55 +4189,55 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>I’m currently a Wells Fargo customer with an open bank account &amp; I was emailed! &amp; I associate with an organization who’s in a partnership with We</t>
+          <t>The Inner Circle powered by Wells Fargo and partnered with Sara Jakes Roberts Woman Evolved.</t>
         </is>
       </c>
       <c r="K64" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>003QP00001Bw5F6</t>
+          <t>003QP000017yg7w</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>McCree</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>manager@pickleforklockandkey.com</t>
+          <t>kree@akwrestlingfoundation.org</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Smith</t>
+          <t>WellsFargo - Feb 26 - McCree</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>District Of Columbia</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Baltimore City Mayor's Office - Small &amp; Minority Business Advocacy &amp; Development</t>
+          <t>Casey Field, Senior Search Manager sent an email to inform me of the opportunity.</t>
         </is>
       </c>
       <c r="K65" s="3" t="b">
@@ -4263,44 +4263,44 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>003QP00000sQBDe</t>
+          <t>003QP00001Ame1h</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Manju</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Rupani</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>manjurupani@outlook.com</t>
+          <t>krwms62@gmail.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Rupani</t>
+          <t>WellsFargo - Feb 26 - Williams</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Wells Fargo Outreach</t>
+          <t>I received an email from the Watson Institute and researched the opportunity further via social media and Wells Fargo’s website.</t>
         </is>
       </c>
       <c r="K66" s="3" t="b">
@@ -4326,59 +4326,59 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/9/2025</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>003QP000016pbZS</t>
+          <t>003QP000019tNpc</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Marilyn</t>
+          <t>Seble</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Berchie-Gialamas</t>
+          <t>Mamo</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>marilyn@trinitymaternalwellness.org</t>
+          <t>laboscience954@gmail.com</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Berchie-Gialamas</t>
+          <t>WellsFargo - Feb 26 - Mamo</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>Contact person: Miss Seble Mamo and organization name: Laboscience Enterprise  YouTube: https://youtube.com/@seblemamo858?si=dbnsTuEbuf5AnT8p</t>
         </is>
       </c>
       <c r="K67" s="3" t="b">
@@ -4389,107 +4389,107 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>003QP00000BiRW5</t>
+          <t>003QP000017x9MC</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Lance</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Murangiri</t>
+          <t>Cabral</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>markmurangiri885@gmail.com</t>
+          <t>lancec@letsfeast.co</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Murangiri</t>
+          <t>WellsFargo - Feb 26 - Cabral</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>opportunities for youth</t>
+          <t>through Instagram</t>
         </is>
       </c>
       <c r="K68" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>11/24/2025</t>
+          <t>11/19/2025</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CkL5F</t>
+          <t>003QP0000169CIy</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Marufa</t>
+          <t>Lathonia</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Bhuiyan</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>marufa@hawaii.edu</t>
+          <t>lathonia@justuscpp.org</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bhuiyan</t>
+          <t>WellsFargo - Feb 26 - Bennett</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4499,55 +4499,55 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>US Minor Outlying Islands</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>I was Googling about Fellowships to join in the USA in 2026, and it appeared on the first page</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="K69" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>11/6/2025</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AC7fR</t>
+          <t>003QP00001Czwao</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Latasha</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Picciola</t>
+          <t>Curry</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>melissap@lanechicago.org</t>
+          <t>lcurry79.lc.lc.lc@gmail.com</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Picciola</t>
+          <t>WellsFargo - Feb 26 - Curry</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>West Side Forward Social media account</t>
+          <t>Feeding The Soul Catering Latasha Curry is the Owner and Manager of the Food Catering</t>
         </is>
       </c>
       <c r="K70" s="3" t="b">
@@ -4578,34 +4578,34 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/23/2025</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>003QP0000197rRi</t>
+          <t>003QP00001AMQtf</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Tanya</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Watyoka</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>michael@growwisewealthybuilders.com</t>
+          <t>legacy2916@gmail.com</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Watyoka</t>
+          <t>WellsFargo - Feb 26 - Taylor</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Howard county</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4625,75 +4625,75 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Casey Margarite Field, Sandra Mancia they work at Watson  Institute ,they  reached out to my wife and my wife shared with me ,she knows that I am bus</t>
+          <t>I received an email invitation from Casey Margarite Field in response to interest from a social media post.</t>
         </is>
       </c>
       <c r="K71" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>003QP00000xXdiD</t>
+          <t>003QP00001DoDoV</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>test n29</t>
+          <t>LeTitia</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>octubre monica</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>monica.solaresdc@gmail.com</t>
+          <t>letitiasmall@tishyspuffs.com</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Undecided - Feb 26 - octubre monica</t>
+          <t>WellsFargo - Feb 26 - Small</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>wsta</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
+          <t>Greater Washington Urban League Center</t>
         </is>
       </c>
       <c r="K72" s="3" t="b">
@@ -4704,97 +4704,97 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/31/2025</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>003QP00000xXdiD</t>
+          <t>003QP00001AMQuv</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>test n29</t>
+          <t>Denika</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>octubre monica</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>monica.solaresdc@gmail.com</t>
+          <t>luvlotsss@yahoo.com</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - octubre monica</t>
+          <t>WellsFargo - Feb 26 - Oliver</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>wsta</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
+          <t>I’m currently a Wells Fargo customer with an open bank account &amp; I was emailed! &amp; I associate with an organization who’s in a partnership with We</t>
         </is>
       </c>
       <c r="K73" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>10/29/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>003QP00001B4NAV</t>
+          <t>003QP00001Bw5F6</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Morenikeji</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ofo</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>morenikeji.ofo@gmail.com</t>
+          <t>manager@pickleforklockandkey.com</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ofo</t>
+          <t>WellsFargo - Feb 26 - Smith</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Md/ North America</t>
+          <t>District Of Columbia</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4819,55 +4819,55 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>I was referred by Harold Booker of the Greater Baltimore Urban League. In 2022, I was a recipient of the Pepsi Black Accelerator Program and consider</t>
+          <t>Baltimore City Mayor's Office - Small &amp; Minority Business Advocacy &amp; Development</t>
         </is>
       </c>
       <c r="K74" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L74" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AAha6</t>
+          <t>003QP00000sQBDe</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Moses</t>
+          <t>Manju</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Rupani</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>moses@mohallcommercialud.com</t>
+          <t>manjurupani@outlook.com</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Hall</t>
+          <t>WellsFargo - Feb 26 - Rupani</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Facebook Ad</t>
+          <t>Wells Fargo Outreach</t>
         </is>
       </c>
       <c r="K75" s="3" t="b">
@@ -4893,44 +4893,44 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>003QP00001C9yX1</t>
+          <t>003QP000016pbZS</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Ebony</t>
+          <t>Marilyn</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Berchie-Gialamas</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>mothersonpurpose@gmail.com</t>
+          <t>marilyn@trinitymaternalwellness.org</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gibson</t>
+          <t>WellsFargo - Feb 26 - Berchie-Gialamas</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>instagram: opportunities for youth</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="K76" s="3" t="b">
@@ -4956,107 +4956,107 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>12/17/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>003QP000018bhdh</t>
+          <t>003QP00000BiRW5</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Gamble</t>
+          <t>Murangiri</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>msgbusiness4@gmail.com</t>
+          <t>markmurangiri885@gmail.com</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gamble</t>
+          <t>WellsFargo - Feb 26 - Murangiri</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>A sponsored ad on facebook.</t>
+          <t>opportunities for youth</t>
         </is>
       </c>
       <c r="K77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>11/23/2025</t>
+          <t>11/24/2025</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AEf6g</t>
+          <t>003QP00001CkL5F</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Atif</t>
+          <t>Marufa</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Tate</t>
+          <t>Bhuiyan</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>musicfuture2010@yahoo.com</t>
+          <t>marufa@hawaii.edu</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Tate</t>
+          <t>WellsFargo - Feb 26 - Bhuiyan</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5066,60 +5066,60 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>I was referred by Greater Washington Urban League</t>
+          <t>I was Googling about Fellowships to join in the USA in 2026, and it appeared on the first page</t>
         </is>
       </c>
       <c r="K78" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>12/4/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CT2Jy</t>
+          <t>003QP00001AC7fR</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>chelsea</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>dormevil</t>
+          <t>Picciola</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>naturalserenityflow@gmail.com</t>
+          <t>melissap@lanechicago.org</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - dormevil</t>
+          <t>WellsFargo - Feb 26 - Picciola</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>I learned about the Wells Fargo Small Business Fellowship through the Watson Institute entrepreneurial ecosystem and small business support network.</t>
+          <t>West Side Forward Social media account</t>
         </is>
       </c>
       <c r="K79" s="3" t="b">
@@ -5145,44 +5145,44 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>12/19/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>003QP000019oMyy</t>
+          <t>003QP0000197rRi</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Nya</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Watyoka</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>nyaemmyco@gmail.com</t>
+          <t>michael@growwisewealthybuilders.com</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Johnson</t>
+          <t>WellsFargo - Feb 26 - Watyoka</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Howard county</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>I saw it on Instagram and clicked for more information</t>
+          <t>Casey Margarite Field, Sandra Mancia they work at Watson  Institute ,they  reached out to my wife and my wife shared with me ,she knows that I am bus</t>
         </is>
       </c>
       <c r="K80" s="3" t="b">
@@ -5208,59 +5208,59 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12/2/2025</t>
+          <t>11/26/2025</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Zdlb</t>
+          <t>003QP00000xXdiD</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>test n29</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>octubre monica</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ojohnson@kok.services</t>
+          <t>monica.solaresdc@gmail.com</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Johnson</t>
+          <t>Undecided - Feb 26 - octubre monica</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>wsta</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Facebook Group: Illinois Small Business Owners Network</t>
+          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
         </is>
       </c>
       <c r="K81" s="3" t="b">
@@ -5271,59 +5271,59 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>003QP00001CryOQ</t>
+          <t>003QP00000xXdiD</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>test n29</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>octubre monica</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>orders@mspsgfree.com</t>
+          <t>monica.solaresdc@gmail.com</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Marsh</t>
+          <t>WellsFargo - Feb 26 - octubre monica</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>wsta</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>I received an email</t>
+          <t>Please elaborate on your answer to the question above.* For example: if referred, (tell us the full name of the person and Organization); if you mar</t>
         </is>
       </c>
       <c r="K82" s="3" t="b">
@@ -5334,122 +5334,122 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>10/29/2025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>003QP000019Qrat</t>
+          <t>003QP00001B4NAV</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Nhlanhla</t>
+          <t>Morenikeji</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Magwaza</t>
+          <t>Ofo</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>president@apasa-npc.org.za</t>
+          <t>morenikeji.ofo@gmail.com</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Magwaza</t>
+          <t>WellsFargo - Feb 26 - Ofo</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Internet Search</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>KwaZulu Natal</t>
+          <t>Md/ North America</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>I found information through Facebook advertising</t>
+          <t>I was referred by Harold Booker of the Greater Baltimore Urban League. In 2022, I was a recipient of the Pepsi Black Accelerator Program and consider</t>
         </is>
       </c>
       <c r="K83" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L83" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>11/29/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>003QP000019E00u</t>
+          <t>003QP00001AAha6</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Moses</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Nyembe</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>rsa.nyembe@gmail.com</t>
+          <t>moses@mohallcommercialud.com</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Nyembe</t>
+          <t>WellsFargo - Feb 26 - Hall</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Gauteng</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Facebook Ad</t>
         </is>
       </c>
       <c r="K84" s="3" t="b">
@@ -5460,44 +5460,44 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>11/27/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>003QP000016y4Qk</t>
+          <t>003QP00001C9yX1</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Ebony</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Gale</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>santanagale214@gmail.com</t>
+          <t>mothersonpurpose@gmail.com</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gale</t>
+          <t>WellsFargo - Feb 26 - Gibson</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5512,50 +5512,50 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>I am subscribed to your email list.</t>
+          <t>instagram: opportunities for youth</t>
         </is>
       </c>
       <c r="K85" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>11/13/2025</t>
+          <t>12/17/2025</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>003QP000019wFp2</t>
+          <t>003QP000018bhdh</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Gamble</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>sean@hustlersmba.com</t>
+          <t>msgbusiness4@gmail.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Long</t>
+          <t>WellsFargo - Feb 26 - Gamble</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>I recieved an email from Casey Field</t>
+          <t>A sponsored ad on facebook.</t>
         </is>
       </c>
       <c r="K86" s="3" t="b">
@@ -5586,59 +5586,59 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>11/23/2025</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>003QP000016GLZM</t>
+          <t>003QP00001DPcV9</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Seke</t>
+          <t>MUDADI</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Ballard</t>
+          <t>SAIDI</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>seke@betascore.ai</t>
+          <t>mudadisaidi@dr.com</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ballard</t>
+          <t>WellsFargo - Feb 26 - SAIDI</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TURKANA  COUNTY</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Congo, Democratic Republic of the</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Lorenzo Thione from Gaingels suggested that I apply.</t>
+          <t>Bridge Builders Hub</t>
         </is>
       </c>
       <c r="K87" s="3" t="b">
@@ -5649,44 +5649,44 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>11/7/2025</t>
+          <t>12/27/2025</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>003QP000003kVao</t>
+          <t>003QP00001AEf6g</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Shana</t>
+          <t>Atif</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>OConners</t>
+          <t>Tate</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>shana@disrupttheimpossible.com</t>
+          <t>musicfuture2010@yahoo.com</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - OConners</t>
+          <t>WellsFargo - Feb 26 - Tate</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5701,45 +5701,45 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Polsky Exchange</t>
+          <t>I was referred by Greater Washington Urban League</t>
         </is>
       </c>
       <c r="K88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>12/4/2025</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>003QP000018FDO5</t>
+          <t>003QP00001CT2Jy</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>chelsea</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>dormevil</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>simonejterry@icloud.com</t>
+          <t>naturalserenityflow@gmail.com</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Terry</t>
+          <t>WellsFargo - Feb 26 - dormevil</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>I learned about the fellowship through an entrepreneurial support network that regularly shares resources and opportunities for small business owners</t>
+          <t>I learned about the Wells Fargo Small Business Fellowship through the Watson Institute entrepreneurial ecosystem and small business support network.</t>
         </is>
       </c>
       <c r="K89" s="3" t="b">
@@ -5775,44 +5775,44 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>12/19/2025</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>003QP000019SXoJ</t>
+          <t>003QP000019oMyy</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Enoch</t>
+          <t>Nya</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>smithenoch3@gmail.com</t>
+          <t>nyaemmyco@gmail.com</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Smith</t>
+          <t>WellsFargo - Feb 26 - Johnson</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>I receive monthly information from Illinois. Grant Watch, and this information was provided for my review.</t>
+          <t>I saw it on Instagram and clicked for more information</t>
         </is>
       </c>
       <c r="K90" s="3" t="b">
@@ -5838,102 +5838,102 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>11/30/2025</t>
+          <t>12/2/2025</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AisuY</t>
+          <t>003QP000019Zdlb</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Gyapong</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>steveagenda1899@gmail.com</t>
+          <t>ojohnson@kok.services</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Gyapong</t>
+          <t>WellsFargo - Feb 26 - Johnson</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Social Media (Non Watson Institute Accounts)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Ashanti</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Facebook Group: Illinois Small Business Owners Network</t>
         </is>
       </c>
       <c r="K91" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L91" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/1/2025</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AfbJz</t>
+          <t>003QP00001CryOQ</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>taylormason@taylorstacoschicago.com</t>
+          <t>orders@mspsgfree.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Mason</t>
+          <t>WellsFargo - Feb 26 - Marsh</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>I heard about this opportunity from Isra Omar from the Polsky Center.</t>
+          <t>I received an email</t>
         </is>
       </c>
       <c r="K92" s="3" t="b">
@@ -5964,122 +5964,122 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>12/8/2025</t>
+          <t>12/22/2025</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BZbMC</t>
+          <t>003QP000019Qrat</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>thomas</t>
+          <t>Nhlanhla</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>christian</t>
+          <t>Magwaza</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>tchrist443@gmail.com</t>
+          <t>president@apasa-npc.org.za</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - christian</t>
+          <t>WellsFargo - Feb 26 - Magwaza</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Internet Search</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Md</t>
+          <t>KwaZulu Natal</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Hvac</t>
+          <t>I found information through Facebook advertising</t>
         </is>
       </c>
       <c r="K93" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>11/29/2025</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AYscs</t>
+          <t>003QP000019E00u</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Terri</t>
+          <t>Prince</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Evans</t>
+          <t>Nyembe</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>terrievans27@gmail.com</t>
+          <t>rsa.nyembe@gmail.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Evans</t>
+          <t>WellsFargo - Feb 26 - Nyembe</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Gauteng</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>I first learned about the Fellowship through the Polsky Center for Entrepreneurship and Innovation. Isra Omar at the Polsky Center shared the opportu</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K94" s="3" t="b">
@@ -6090,39 +6090,39 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>12/7/2025</t>
+          <t>11/27/2025</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>003QP00001AMQbh</t>
+          <t>003QP000016y4Qk</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Glenda</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Gale</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>thecititeam@thecitilife.com</t>
+          <t>santanagale214@gmail.com</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Lee</t>
+          <t>WellsFargo - Feb 26 - Gale</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurial Support Organization or Network</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Baltimore City's Mayor's Office of Small and Minority Business Advocacy and Development Email dated December 12, 2025</t>
+          <t>I am subscribed to your email list.</t>
         </is>
       </c>
       <c r="K95" s="3" t="b">
@@ -6153,44 +6153,44 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>12/16/2025</t>
+          <t>11/13/2025</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>003QP00001BGk4x</t>
+          <t>003QP000019wFp2</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Bridgers</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>thecollectivesoul369@gmail.com</t>
+          <t>sean@hustlersmba.com</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Bridgers</t>
+          <t>WellsFargo - Feb 26 - Long</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Anita Sewell</t>
+          <t>I recieved an email from Casey Field</t>
         </is>
       </c>
       <c r="K96" s="3" t="b">
@@ -6216,44 +6216,44 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/3/2025</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>003QP00000SLZB5</t>
+          <t>003QP000016GLZM</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Ticina</t>
+          <t>Seke</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Ballard</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>ticina@creativiticustom.com</t>
+          <t>seke@betascore.ai</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Williams</t>
+          <t>WellsFargo - Feb 26 - Ballard</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6268,55 +6268,55 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>I was sent an email by the Watson Institute to apply.</t>
+          <t>Lorenzo Thione from Gaingels suggested that I apply.</t>
         </is>
       </c>
       <c r="K97" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="3" t="b">
         <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/7/2025</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>003QP000011Hc2z</t>
+          <t>003QP000003kVao</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Shana</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>OConners</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>tom@peakampinstruments.com</t>
+          <t>shana@disrupttheimpossible.com</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Wright</t>
+          <t>WellsFargo - Feb 26 - OConners</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>I learned about the fellowship through a colleague who knew I was working on data center maintenance technology and recommended I explore opportuniti</t>
+          <t>Polsky Exchange</t>
         </is>
       </c>
       <c r="K98" s="3" t="b">
@@ -6342,44 +6342,44 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>12/16/2025</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>003QP000019ZPFa</t>
+          <t>003QP000018FDO5</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>transportation@kneservies.com</t>
+          <t>simonejterry@icloud.com</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Johnson</t>
+          <t>WellsFargo - Feb 26 - Terry</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Social Media (Non Watson Institute Accounts)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Just an advertising on Facebook.</t>
+          <t>I learned about the fellowship through an entrepreneurial support network that regularly shares resources and opportunities for small business owners</t>
         </is>
       </c>
       <c r="K99" s="3" t="b">
@@ -6405,44 +6405,44 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>12/1/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>003QP000017hZik</t>
+          <t>003QP000019SXoJ</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Trezell</t>
+          <t>Enoch</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Ragas</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>trezell@ragasconsulting.com</t>
+          <t>smithenoch3@gmail.com</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Ragas</t>
+          <t>WellsFargo - Feb 26 - Smith</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Word of Mouth (Friend, Family, Colleague)</t>
+          <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6457,144 +6457,900 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Gloria Nauden, Co-Founder, DC COMMUNITY DEVELOPMENT CONSORTIUM  It was sent to her by Casey Margarite Field and Sandra Mancia from Watson Institute</t>
+          <t>I receive monthly information from Illinois. Grant Watch, and this information was provided for my review.</t>
         </is>
       </c>
       <c r="K100" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>11/30/2025</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>0033h00001K7vgw</t>
+          <t>003QP00001AisuY</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Urassa</t>
+          <t>Gyapong</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>urassastanley89@gmail.com</t>
+          <t>steveagenda1899@gmail.com</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>WellsFargo - Feb 26 - Urassa</t>
+          <t>WellsFargo - Feb 26 - Gyapong</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Kilimanjaro</t>
+          <t>Ashanti</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Tanzania, the United Republic of</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Tanzania, the United Republic of</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Stanley urassa,  SETHI URA COMPANY LIMITED</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="K101" s="3" t="b">
         <v>0</v>
       </c>
       <c r="L101" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>11/26/2025</t>
+          <t>12/8/2025</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>003QP00001AfbJz</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>taylormason@taylorstacoschicago.com</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Mason</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>I heard about this opportunity from Isra Omar from the Polsky Center.</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>12/8/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001BZbMC</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>thomas</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>christian</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>tchrist443@gmail.com</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - christian</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Md</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Hvac</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001Brocu</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Pan</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>team@fundingbreakthroughlab.org</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Pan</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>I'm working with an organization that supports non-profits and impact organizations search for and apply to grants grav.id</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L104" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>12/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AYscs</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Terri</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Evans</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>terrievans27@gmail.com</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Evans</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>I first learned about the Fellowship through the Polsky Center for Entrepreneurship and Innovation. Isra Omar at the Polsky Center shared the opportu</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>12/7/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001AMQbh</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Glenda</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>thecititeam@thecitilife.com</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Lee</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Support Organization or Network</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Baltimore City's Mayor's Office of Small and Minority Business Advocacy and Development Email dated December 12, 2025</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L106" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>12/16/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001BGk4x</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Bridgers</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>thecollectivesoul369@gmail.com</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Bridgers</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Anita Sewell</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>003QP00000SLZB5</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Ticina</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>ticina@creativiticustom.com</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Williams</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Watson Institute Channels (Alumni, Staff, Social Media, Email)</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>I was sent an email by the Watson Institute to apply.</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L108" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>003QP000011Hc2z</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>tom@peakampinstruments.com</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Wright</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>il</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>I learned about the fellowship through a colleague who knew I was working on data center maintenance technology and recommended I explore opportuniti</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L109" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>003QP000019ZPFa</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>transportation@kneservies.com</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Johnson</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Social Media (Non Watson Institute Accounts)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Just an advertising on Facebook.</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>12/1/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>003QP000017hZik</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Trezell</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Ragas</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>trezell@ragasconsulting.com</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Ragas</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Word of Mouth (Friend, Family, Colleague)</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Gloria Nauden, Co-Founder, DC COMMUNITY DEVELOPMENT CONSORTIUM  It was sent to her by Casey Margarite Field and Sandra Mancia from Watson Institute</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L111" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>0033h00001K7vgw</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Stanley</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Urassa</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>urassastanley89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Urassa</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Kilimanjaro</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania, the United Republic of</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Tanzania, the United Republic of</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Stanley urassa,  SETHI URA COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>11/26/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>003QP00001AhhEq</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Paula</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>Tripp</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>yourvipbox2024@gmail.com</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>WellsFargo - Feb 26 - Tripp</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Entrepreneurial Support Organization or Network</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>Polsky Center at the University of Chicago</t>
         </is>
       </c>
-      <c r="K102" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
+      <c r="K113" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>12/8/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>003QP00001DVIok</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Abobaker</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Babakarkhil</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>zalandabobaker5@gmail.com</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>WellsFargo - Feb 26 - Babakarkhil</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Opportunity &amp; Fellowship Platforms (Opportunity Desk, ProFellow, Youth Opportunities etc.)</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Kabul</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>UN Millinum Fellow</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L114" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>12/29/2025</t>
         </is>
       </c>
     </row>
